--- a/plantilla_oi.xlsx
+++ b/plantilla_oi.xlsx
@@ -14270,7 +14270,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Z31"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.19921875" customWidth="1" style="198" min="1" max="1"/>
@@ -15740,52 +15740,52 @@
   <sheetData>
     <row r="1" ht="14" customHeight="1" s="198">
       <c r="A1" s="123" t="n"/>
-      <c r="B1" s="124" t="inlineStr"/>
-      <c r="C1" s="124" t="inlineStr"/>
-      <c r="D1" s="124" t="inlineStr"/>
-      <c r="E1" s="124" t="inlineStr"/>
-      <c r="F1" s="124" t="inlineStr"/>
+      <c r="B1" s="124" t="n"/>
+      <c r="C1" s="124" t="n"/>
+      <c r="D1" s="124" t="n"/>
+      <c r="E1" s="124" t="n"/>
+      <c r="F1" s="124" t="n"/>
       <c r="G1" s="124" t="n"/>
       <c r="H1" s="124" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1" s="198">
-      <c r="A2" s="124" t="inlineStr"/>
+      <c r="A2" s="124" t="n"/>
       <c r="B2" s="134" t="inlineStr">
         <is>
           <t>Specs Televisa Ads</t>
         </is>
       </c>
-      <c r="C2" s="124" t="inlineStr"/>
+      <c r="C2" s="124" t="n"/>
       <c r="D2" s="124" t="n"/>
       <c r="E2" s="126" t="n"/>
-      <c r="F2" s="124" t="inlineStr"/>
+      <c r="F2" s="124" t="n"/>
       <c r="G2" s="124" t="n"/>
       <c r="H2" s="124" t="n"/>
     </row>
     <row r="3" ht="14" customHeight="1" s="198">
-      <c r="A3" s="124" t="inlineStr"/>
+      <c r="A3" s="124" t="n"/>
       <c r="B3" s="135" t="inlineStr">
         <is>
           <t>Última actualización: 25 de Septiembre 2023</t>
         </is>
       </c>
-      <c r="C3" s="124" t="inlineStr"/>
+      <c r="C3" s="124" t="n"/>
       <c r="D3" s="124" t="n"/>
       <c r="E3" s="124" t="n"/>
-      <c r="F3" s="124" t="inlineStr"/>
+      <c r="F3" s="124" t="n"/>
       <c r="G3" s="124" t="n"/>
       <c r="H3" s="124" t="n"/>
     </row>
     <row r="4" ht="14" customHeight="1" s="198">
-      <c r="A4" s="127" t="inlineStr"/>
-      <c r="B4" s="127" t="inlineStr"/>
-      <c r="C4" s="127" t="inlineStr"/>
-      <c r="D4" s="127" t="inlineStr"/>
-      <c r="E4" s="127" t="inlineStr"/>
-      <c r="F4" s="127" t="inlineStr"/>
+      <c r="A4" s="127" t="n"/>
+      <c r="B4" s="127" t="n"/>
+      <c r="C4" s="127" t="n"/>
+      <c r="D4" s="127" t="n"/>
+      <c r="E4" s="127" t="n"/>
+      <c r="F4" s="127" t="n"/>
     </row>
     <row r="5" ht="41.25" customHeight="1" s="198">
-      <c r="A5" s="127" t="inlineStr"/>
+      <c r="A5" s="127" t="n"/>
       <c r="B5" s="262" t="inlineStr">
         <is>
           <t>PRODUCT</t>
@@ -16024,7 +16024,7 @@
       </c>
     </row>
     <row r="9" ht="89.25" customHeight="1" s="198">
-      <c r="A9" s="127" t="inlineStr"/>
+      <c r="A9" s="127" t="n"/>
       <c r="B9" s="138" t="inlineStr">
         <is>
           <t>FORMATOS PERMITIDOS</t>
@@ -16125,7 +16125,7 @@
       </c>
     </row>
     <row r="10" ht="84.75" customHeight="1" s="198">
-      <c r="A10" s="127" t="inlineStr"/>
+      <c r="A10" s="127" t="n"/>
       <c r="B10" s="138" t="inlineStr">
         <is>
           <t>DURACIÓN MÁXIMA</t>
@@ -16289,7 +16289,7 @@
       </c>
     </row>
     <row r="12" ht="48.75" customHeight="1" s="198">
-      <c r="A12" s="127" t="inlineStr"/>
+      <c r="A12" s="127" t="n"/>
       <c r="B12" s="138" t="inlineStr">
         <is>
           <t>CLICK THROUGH</t>
@@ -16681,11 +16681,7 @@
     <row r="67" ht="15.75" customHeight="1" s="198"/>
     <row r="68" ht="15.75" customHeight="1" s="198"/>
     <row r="69" ht="15.75" customHeight="1" s="198">
-      <c r="B69" s="127" t="inlineStr">
-        <is>
-          <t>.</t>
-        </is>
-      </c>
+      <c r="B69" s="127" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="198"/>
     <row r="71" ht="15.75" customHeight="1" s="198"/>
